--- a/guru99_automation/src/test/resources/testdata/NewAccount.xlsx
+++ b/guru99_automation/src/test/resources/testdata/NewAccount.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shahr\eclipse-workspace\wipro-assignment\capstone_guru99\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro_capstone\guru99_capstone\guru99_automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2383FBB7-1984-488F-A4B4-4F0A11A584CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6256AB9-EC02-440A-AD76-1A9A1B1CE872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="accountData" sheetId="1" r:id="rId1"/>
@@ -396,7 +396,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>8000</v>
+        <v>28000</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>

--- a/guru99_automation/src/test/resources/testdata/NewAccount.xlsx
+++ b/guru99_automation/src/test/resources/testdata/NewAccount.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro_capstone\guru99_capstone\guru99_automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6256AB9-EC02-440A-AD76-1A9A1B1CE872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFDF1D7-87BD-4A12-A6C9-C1A833CAC0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="1935" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="accountData" sheetId="1" r:id="rId1"/>
@@ -390,7 +390,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>33840</v>
+        <v>9660</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -404,7 +404,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>11813</v>
+        <v>5792</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>33840</v>
+        <v>9660</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -432,7 +432,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>11813</v>
+        <v>5792</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -446,7 +446,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>33840</v>
+        <v>9660</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
